--- a/output/pdf_financials_xlsx/MTX.xlsx
+++ b/output/pdf_financials_xlsx/MTX.xlsx
@@ -5569,46 +5569,46 @@
         <v>15.027625</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>11.579389</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>10.527813</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>10.423784</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>9.677724</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>9.487666000000001</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>9.498666</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>9.498666</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>9.487666000000001</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>9.261879</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>7.805988</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>7.823871</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>8.404439999999999</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>8.124851</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>8.088881000000001</v>
       </c>
     </row>
     <row r="93">
@@ -9226,7 +9226,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="n">
         <v>12.068418</v>
       </c>
@@ -9736,7 +9740,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -10200,7 +10208,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -11372,7 +11384,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MTX.xlsx
+++ b/output/pdf_financials_xlsx/MTX.xlsx
@@ -999,52 +999,52 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.040861</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.085951</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.184202</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.130734</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.057353</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.035697</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.016505</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.010106</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.015207</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.02495</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.025196</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.004305</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.012691</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.13523</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.071538</v>
       </c>
     </row>
     <row r="13">
@@ -1908,52 +1908,52 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-15.741095</v>
+        <v>-15.781956</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-9.013825000000001</v>
+        <v>-9.099776</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-7.20189</v>
+        <v>-7.386092</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-8.922526</v>
+        <v>-9.05326</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.958216</v>
+        <v>-4.015569</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.100642</v>
+        <v>-2.136339</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.232579</v>
+        <v>-1.249084</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.777798</v>
+        <v>-0.787904</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.760072</v>
+        <v>0.744865</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.04044</v>
+        <v>-0.06539</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.88462</v>
+        <v>0.859424</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.006483</v>
+        <v>-1.010788</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.587112</v>
+        <v>1.574421</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.217608</v>
+        <v>-1.304108</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-2.568455</v>
+        <v>-2.703685</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0.429094</v>
+        <v>0.357556</v>
       </c>
     </row>
     <row r="28">
@@ -2018,52 +2018,52 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-15.741095</v>
+        <v>-15.781956</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-8.993285</v>
+        <v>-9.079236</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-7.147981</v>
+        <v>-7.332183</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-8.857711999999999</v>
+        <v>-8.988446</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.89428</v>
+        <v>-3.951633</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.074109</v>
+        <v>-2.109806</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.232579</v>
+        <v>-1.249084</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.777798</v>
+        <v>-0.787904</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.760072</v>
+        <v>0.744865</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.04044</v>
+        <v>-0.06539</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.88589</v>
+        <v>0.860694</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.005092</v>
+        <v>-1.009397</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>1.588834</v>
+        <v>1.576143</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.21715</v>
+        <v>-1.30365</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.568111</v>
+        <v>-2.703341</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.429094</v>
+        <v>0.357556</v>
       </c>
     </row>
     <row r="30">
@@ -2309,52 +2309,52 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>8.926728000000001</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>18.153497</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>15.507491</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>3.693555</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>3.385044</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.630815</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.799712</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.707516</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.54266</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.406261</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.275853</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>2.264936</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.739733</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>2.323345</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.422113</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>1.118058</v>
       </c>
     </row>
     <row r="35">
@@ -2419,52 +2419,52 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>8.926728000000001</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>18.153497</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>15.507491</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>3.693555</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>3.385044</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.630815</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.799712</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.707516</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.54266</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.406261</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.275853</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>2.264936</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.739733</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>2.323345</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.422113</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>1.118058</v>
       </c>
     </row>
     <row r="37">
@@ -3079,52 +3079,52 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>9.906470000000001</v>
+        <v>0.979742</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>18.423622</v>
+        <v>0.270125</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>15.666257</v>
+        <v>0.158766</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>7.231113</v>
+        <v>3.537558</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.425702</v>
+        <v>0.040658</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.658145</v>
+        <v>0.02733</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.858899</v>
+        <v>0.059187</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.744108</v>
+        <v>0.036592</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.572942</v>
+        <v>0.030282</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.426948</v>
+        <v>0.020687</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.294575</v>
+        <v>0.018722</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.495106</v>
+        <v>0.23017</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.7627969999999999</v>
+        <v>0.023064</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>2.345157</v>
+        <v>0.021812</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.448235</v>
+        <v>0.026122</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>1.142831</v>
+        <v>0.024773</v>
       </c>
     </row>
     <row r="49">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -8576,7 +8576,11 @@
           <t>Reclamation deposit 6</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -10570,7 +10574,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -12140,7 +12148,11 @@
           <t>Reclamation deposit 5</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -12334,7 +12346,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
@@ -13676,7 +13688,11 @@
           <t>Interest accrued on reclamation deposit</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -17350,7 +17366,11 @@
           <t>Interest (accrued) reversed on reclamation deposit</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -21000,7 +21020,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -25790,7 +25814,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -30412,7 +30436,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -32484,7 +32508,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -36770,7 +36794,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E310" s="5" t="n">

--- a/output/pdf_financials_xlsx/MTX.xlsx
+++ b/output/pdf_financials_xlsx/MTX.xlsx
@@ -745,31 +745,31 @@
         <v>0.182741</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.071274</v>
+        <v>0.130038</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.116674</v>
+        <v>0.142079</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.131133</v>
+        <v>0.191133</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.123352</v>
+        <v>0.183352</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.152177</v>
+        <v>0.212177</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.091874</v>
+        <v>0.151874</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.158537</v>
+        <v>0.218537</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.203976</v>
+        <v>0.263976</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.158375</v>
+        <v>0.218375</v>
       </c>
     </row>
     <row r="8">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>3.825</v>
+        <v>-3.825</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.15853</v>
+        <v>-1.49905</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -2163,7 +2163,7 @@
         <v>-24.29945311936685</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-1.758742820056968</v>
+        <v>-16.63056471586702</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -4156,46 +4156,46 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.34303</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.348737</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.40188</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.945221</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.108286</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.176463</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.175134</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.199389</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.224794</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.284794</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.344794</v>
       </c>
       <c r="M67" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.451669</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.0034</v>
       </c>
       <c r="P67" s="3" t="n">
         <v>0</v>
@@ -6560,13 +6560,13 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001538</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.060198</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.133336</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -6593,10 +6593,10 @@
         <v>0</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001443</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>6.999999999999999e-05</v>
       </c>
       <c r="O111" s="3" t="n">
         <v>0</v>
@@ -7865,13 +7865,13 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001538</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.060198</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.133336</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -7898,10 +7898,10 @@
         <v>0</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001443</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-6.999999999999999e-05</v>
       </c>
       <c r="O134" s="3" t="n">
         <v>0</v>
@@ -7920,13 +7920,13 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-18.139487</v>
+        <v>-18.141025</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-7.792803</v>
+        <v>-7.853001</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-7.247808</v>
+        <v>-7.381144</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-7.407736</v>
@@ -7953,10 +7953,10 @@
         <v>-0.126596</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-0.889317</v>
+        <v>-0.89076</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-1.776273</v>
+        <v>-1.776343</v>
       </c>
       <c r="O135" s="3" t="n">
         <v>-0.520275</v>
@@ -16886,7 +16886,11 @@
           <t>Rebate on (purchase of) equipment</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -21508,7 +21512,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -22962,7 +22970,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E163" s="5" t="n">
         <v>-3.825</v>
       </c>
@@ -23540,7 +23552,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E169" s="5" t="n">
         <v>-0.001538</v>
       </c>
@@ -24890,7 +24906,11 @@
           <t>Directors fees 10</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -29382,7 +29402,11 @@
           <t>Directors fees 9</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -37276,7 +37300,11 @@
           <t>Future income tax recovery (Note 8)</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E315" s="5" t="n">
         <v>3.825</v>
       </c>
